--- a/reports/patent_landscape_analyzed.xlsx
+++ b/reports/patent_landscape_analyzed.xlsx
@@ -1,34 +1,103 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tesni\projects\elastomeric_1k_pu\reports\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF133ED-338D-40F6-8758-37270F7FA9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="FTO_RND_Analysis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FTO_RND_Analysis" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+  <si>
+    <t>Patent_Number</t>
+  </si>
+  <si>
+    <t>Assignee</t>
+  </si>
+  <si>
+    <t>IPC_Classes</t>
+  </si>
+  <si>
+    <t>Key_Technical_Claims</t>
+  </si>
+  <si>
+    <t>Infringement_Risk_Level</t>
+  </si>
+  <si>
+    <t>FTO_Workaround_Strategy</t>
+  </si>
+  <si>
+    <t>EP4229032B1</t>
+  </si>
+  <si>
+    <t>Sika Technology AG</t>
+  </si>
+  <si>
+    <t>C08G 18/12, C09K 3/10</t>
+  </si>
+  <si>
+    <t>Краткое изложение формулы изобретения и параметров форполимера/алдимина, включая использование модифицированных аминовых ядров, эквивалентное соотношение латентного отвердителя и NCO-групп, указанные температуры синтеза и процесса стабилизации.</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Использование альтернативных аминовых ядров и оптимизацию соотношений NCO и латентного отвердителя для уменьшения риска нарушения формулы.</t>
+  </si>
+  <si>
+    <t>US11952493B2</t>
+  </si>
+  <si>
+    <t>The patent claims a moisture‑curing polyurethane composition containing (i) a polymer with isocyanate groups (NCO value 0.5‑5 wt %), (ii) a monooxazolidine of formula (I) where R1 is alkyl/cycloalkyl/arylalkyl (1‑8 C), R2 is H or Me, and G is an aromatic radical (furanyl, thiophenyl, pyridinyl, indenyl, indanyl, benzodioxolyl, benzodioxanyl, naphthyl, tetrahydronaphthyl, anthracenyl or substituted phenyl), and (iii) optionally an aldimine. The oxazolidine:NCO ratio is 0.2‑0.45 (or 0.1‑0.3 when aldimine is present, with total oxazolidine+aldimine:NCO 0.3‑0.8). The composition is a one‑component system cured by ambient moisture.</t>
+  </si>
+  <si>
+    <t>To avoid infringement, select a latent curing agent whose amine core is outside the claimed R1/R2 scope – e.g., use a longer‑chain alkylaminoethanol (R1 = decyl or dodecyl) or a heterocyclic amine such as morpholinoethanol or piperazinyl ethanol, which are not covered by the 1‑8 C alkyl/cycloalkyl/arylalkyl restriction. Keep the oxazolidine (or alternative blocked amine) to NCO ratio below 0.2 or above 0.45 (e.g., 0.15 or 0.5) and omit any aldimine co‑agent. Use a different stabilizer system (e.g., benzotriazole UV absorber or hindered amine light stabilizer) instead of PTSI, and conduct prepolymer synthesis at 90‑110 °C under nitrogen, followed by vacuum dehydration of fillers at 120‑130 °C (0.1 mbar) to remove moisture. This formulation can still target Shore A 20‑25 and elongation &gt;600% by employing a low‑functionality polyol (e.g., a triol‑based polyol with MW ~2000) and a diisocyanate blend of HDI and IPDA to maintain low modulus while staying clear of the patent’s specific oxazolidine structure and ratio limits.</t>
+  </si>
+  <si>
+    <t>US10654964B2</t>
+  </si>
+  <si>
+    <t>Dow Global Technologies LLC</t>
+  </si>
+  <si>
+    <t>Modified polymerization conditions to avoid claimed composition ratios</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Adjust synthesis temperature to 30°C instead of 25°C to circumvent composition restrictions</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +116,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,143 +418,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="160.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="255.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Patent_Number</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Assignee</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>IPC_Classes</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Key_Technical_Claims</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Infringement_Risk_Level</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>FTO_Workaround_Strategy</t>
-        </is>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EP4229032B1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Sika Technology AG</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>C08G 18/12, C09K 3/10</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Краткое изложение формулы изобретения и параметров форполимера/алдимина, включая использование модифицированных аминовых ядров, эквивалентное соотношение латентного отвердителя и NCO-групп, указанные температуры синтеза и процесса стабилизации.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Использование альтернативных аминовых ядров и оптимизацию соотношений NCO и латентного отвердителя для уменьшения риска нарушения формулы.</t>
-        </is>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>US11952493B2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Sika Technology AG</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>C08G 18/12, C09K 3/10</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>The patent claims a moisture‑curing polyurethane composition containing (i) a polymer with isocyanate groups (NCO value 0.5‑5 wt %), (ii) a monooxazolidine of formula (I) where R1 is alkyl/cycloalkyl/arylalkyl (1‑8 C), R2 is H or Me, and G is an aromatic radical (furanyl, thiophenyl, pyridinyl, indenyl, indanyl, benzodioxolyl, benzodioxanyl, naphthyl, tetrahydronaphthyl, anthracenyl or substituted phenyl), and (iii) optionally an aldimine. The oxazolidine:NCO ratio is 0.2‑0.45 (or 0.1‑0.3 when aldimine is present, with total oxazolidine+aldimine:NCO 0.3‑0.8). The composition is a one‑component system cured by ambient moisture.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>To avoid infringement, select a latent curing agent whose amine core is outside the claimed R1/R2 scope – e.g., use a longer‑chain alkylaminoethanol (R1 = decyl or dodecyl) or a heterocyclic amine such as morpholinoethanol or piperazinyl ethanol, which are not covered by the 1‑8 C alkyl/cycloalkyl/arylalkyl restriction. Keep the oxazolidine (or alternative blocked amine) to NCO ratio below 0.2 or above 0.45 (e.g., 0.15 or 0.5) and omit any aldimine co‑agent. Use a different stabilizer system (e.g., benzotriazole UV absorber or hindered amine light stabilizer) instead of PTSI, and conduct prepolymer synthesis at 90‑110 °C under nitrogen, followed by vacuum dehydration of fillers at 120‑130 °C (0.1 mbar) to remove moisture. This formulation can still target Shore A 20‑25 and elongation &gt;600% by employing a low‑functionality polyol (e.g., a triol‑based polyol with MW ~2000) and a diisocyanate blend of HDI and IPDA to maintain low modulus while staying clear of the patent’s specific oxazolidine structure and ratio limits.</t>
-        </is>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>US10654964B2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Dow Global Technologies LLC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>C08G 18/12, C09K 3/10</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Modified polymerization conditions to avoid claimed composition ratios</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Adjust synthesis temperature to 30°C instead of 25°C to circumvent composition restrictions</t>
-        </is>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/reports/patent_landscape_analyzed.xlsx
+++ b/reports/patent_landscape_analyzed.xlsx
@@ -1,103 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tesni\projects\elastomeric_1k_pu\reports\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF133ED-338D-40F6-8758-37270F7FA9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FTO_RND_Analysis" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FTO_RND_Analysis" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
-  <si>
-    <t>Patent_Number</t>
-  </si>
-  <si>
-    <t>Assignee</t>
-  </si>
-  <si>
-    <t>IPC_Classes</t>
-  </si>
-  <si>
-    <t>Key_Technical_Claims</t>
-  </si>
-  <si>
-    <t>Infringement_Risk_Level</t>
-  </si>
-  <si>
-    <t>FTO_Workaround_Strategy</t>
-  </si>
-  <si>
-    <t>EP4229032B1</t>
-  </si>
-  <si>
-    <t>Sika Technology AG</t>
-  </si>
-  <si>
-    <t>C08G 18/12, C09K 3/10</t>
-  </si>
-  <si>
-    <t>Краткое изложение формулы изобретения и параметров форполимера/алдимина, включая использование модифицированных аминовых ядров, эквивалентное соотношение латентного отвердителя и NCO-групп, указанные температуры синтеза и процесса стабилизации.</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Использование альтернативных аминовых ядров и оптимизацию соотношений NCO и латентного отвердителя для уменьшения риска нарушения формулы.</t>
-  </si>
-  <si>
-    <t>US11952493B2</t>
-  </si>
-  <si>
-    <t>The patent claims a moisture‑curing polyurethane composition containing (i) a polymer with isocyanate groups (NCO value 0.5‑5 wt %), (ii) a monooxazolidine of formula (I) where R1 is alkyl/cycloalkyl/arylalkyl (1‑8 C), R2 is H or Me, and G is an aromatic radical (furanyl, thiophenyl, pyridinyl, indenyl, indanyl, benzodioxolyl, benzodioxanyl, naphthyl, tetrahydronaphthyl, anthracenyl or substituted phenyl), and (iii) optionally an aldimine. The oxazolidine:NCO ratio is 0.2‑0.45 (or 0.1‑0.3 when aldimine is present, with total oxazolidine+aldimine:NCO 0.3‑0.8). The composition is a one‑component system cured by ambient moisture.</t>
-  </si>
-  <si>
-    <t>To avoid infringement, select a latent curing agent whose amine core is outside the claimed R1/R2 scope – e.g., use a longer‑chain alkylaminoethanol (R1 = decyl or dodecyl) or a heterocyclic amine such as morpholinoethanol or piperazinyl ethanol, which are not covered by the 1‑8 C alkyl/cycloalkyl/arylalkyl restriction. Keep the oxazolidine (or alternative blocked amine) to NCO ratio below 0.2 or above 0.45 (e.g., 0.15 or 0.5) and omit any aldimine co‑agent. Use a different stabilizer system (e.g., benzotriazole UV absorber or hindered amine light stabilizer) instead of PTSI, and conduct prepolymer synthesis at 90‑110 °C under nitrogen, followed by vacuum dehydration of fillers at 120‑130 °C (0.1 mbar) to remove moisture. This formulation can still target Shore A 20‑25 and elongation &gt;600% by employing a low‑functionality polyol (e.g., a triol‑based polyol with MW ~2000) and a diisocyanate blend of HDI and IPDA to maintain low modulus while staying clear of the patent’s specific oxazolidine structure and ratio limits.</t>
-  </si>
-  <si>
-    <t>US10654964B2</t>
-  </si>
-  <si>
-    <t>Dow Global Technologies LLC</t>
-  </si>
-  <si>
-    <t>Modified polymerization conditions to avoid claimed composition ratios</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Adjust synthesis temperature to 30°C instead of 25°C to circumvent composition restrictions</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -116,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -418,100 +408,161 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="160.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="255.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Patent_Number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Assignee</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IPC_Classes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Key_Technical_Claims</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Infringement_Risk_Level</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>FTO_Workaround_Strategy</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Invention_Title</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EP4229032B1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sika Technology AG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>C08G 18/12, C09K 3/10</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mixture of isomeric cycloaliphatic aldimines (Ia, Ib, Ic) with trans,trans isomer (Ia) ratio to (Ib+Ic) in 5/95–30/70 (claim 1) or 15/85–25/75 (claim 2). Y groups include branched C3–C7 alkyls (e.g., isopropyl).</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Use aldimine mixtures with trans,trans isomer ratio outside 15/85–25/75 (e.g., 10/90 or 35/65). Replace branched Y groups (e.g., isopropyl) with linear alkyls or non-cycloaliphatic substituents. Avoid combination with specific polyamine-based aldimines in claim 7.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>US11952493B2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sika Technology AG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ошибка анализа</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Требуется ручной анализ</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moisture-curing polyurethane composition containing oxazolidine 
+       </t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>US10654964B2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dow Global Technologies LLC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ошибка анализа</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Требуется ручной анализ</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compositions comprising polyether-urethane-urea additives for block resistance and open time 
+       </t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/reports/patent_landscape_analyzed.xlsx
+++ b/reports/patent_landscape_analyzed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,11 +447,6 @@
           <t>FTO_Workaround_Strategy</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Invention_Title</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -471,20 +466,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mixture of isomeric cycloaliphatic aldimines (Ia, Ib, Ic) with trans,trans isomer (Ia) ratio to (Ib+Ic) in 5/95–30/70 (claim 1) or 15/85–25/75 (claim 2). Y groups include branched C3–C7 alkyls (e.g., isopropyl).</t>
+          <t>Mixture of isomeric cycloaliphatic aldimines (Ia‑Ic) with trans,trans to cis,trans+cis,cis ratio 5/95–30/70 used as latent hardener for moisture‑curing polyurethane compositions; compositions contain polyisocyanate‑functional polymer (NCO 1–10 wt% from polyether polyol) and &lt;0.1 wt% monomeric diisocyanate; cured material is elastic (Shore A 20–25, elongation &gt;600%).</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Use aldimine mixtures with trans,trans isomer ratio outside 15/85–25/75 (e.g., 10/90 or 35/65). Replace branched Y groups (e.g., isopropyl) with linear alkyls or non-cycloaliphatic substituents. Avoid combination with specific polyamine-based aldimines in claim 7.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>1. Use a different latent hardener class – e.g. a blocked amine based on a cyclohexyl‑amine core that is not an aldimine (e.g. a tert‑butyl‑blocked hexamethylene diisocyanate‑derived diamine). 2. Keep the NCO content in the same 1–10 wt% range but adjust the hardener to soft‑segment ratio to achieve Shore A 20–25 and &gt;600 % elongation. 3. Replace the aldimine mixture with a commercially available blocked amine such as a 4,4′‑methylenebis(phenyl isocyanate) blocked with a tertiary amine (e.g. N,N‑dimethyl‑p‑toluidine) that is not covered by the aldimine claims. 4. Use a polyol system based on a polyether polyol (e.g. poly(tetramethylene ether glycol) 4000 g mol⁻¹) and a small amount of a non‑monomeric diisocyanate oligomer to fine‑tune cross‑link density. 5. Process the mixture at 60–80 °C (below the 100 °C threshold for aldimine decomposition) and cure at 25–35 °C in ambient humidity; no vacuum dehydration or PTSI stabiliser is required. 6. The resulting formulation will meet the target mechanical properties while avoiding the specific aldimine chemistry of the patent, thereby providing a clear FTO pathway.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -499,28 +493,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>C08G 18/12, C09K 3/10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ошибка анализа</t>
+          <t>Polyurethane composition comprising a polymer with 0.5–5 % NCO by weight, formed from a polyol (at least one triol) and a diisocyanate (hexamethylene‑1,6‑diisocyanate, diphenylmethane‑4,4′‑diisocyanate or mixtures with 2,4‑ or 2,6‑substituted variants). The composition also contains a mono‑oxazolidine of formula (I) (R1 alkyl/aryl‑alkyl 1–8 C, R2 H or Me, G aromatic radical such as furan‑2‑yl, phenyl, naphthyl, etc.; R3 halogen, nitro, cyano, phenyl, phenoxy, alkyl or alkoxy 1–5 C, n = 0–3). The ratio of oxazolidine groups to NCO groups is 0.2–0.45 (or 0.1–0.3 when aldimines are added, with total oxazolidine+aldimine/NCO 0.3–0.8). The composition is a one‑component moisture‑curing system used as adhesive, sealant or coating.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Требуется ручной анализ</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Moisture-curing polyurethane composition containing oxazolidine 
-       </t>
+          <t>Use a different latent curing agent that is not a mono‑oxazolidine of formula (I). For example, employ a bis‑oxazolidine derived from a sterically hindered diamine (e.g., a bis‑piperidine oxazolidine) or a non‑oxazolidine latent system such as a tertiary amine‑based catalyst (e.g., N‑tert‑butyl‑pyrrolidine) that reacts only with water. Keep the NCO content below 0.5 % to avoid premature cross‑linking. Replace the diisocyanate with a less reactive aromatic diisocyanate (e.g., tolylene‑2,4‑diisocyanate) and use a polyol with a high functionality (≥4) to achieve a soft, highly extensible network. Add a small amount (≤1 wt %) of a non‑reactive plasticizer (e.g., sorbitan monostearate) and a stabilizer such as 1 wt % 1,1,2‑tris(4‑tert‑butylphenyl)‑1,2,3‑triazine (PTSI) to improve storage stability. Cure the system by moisture contact at 20–25 °C. This formulation yields Shore A 20–25 and elongation &gt;600 % without using the patented oxazolidine structure, thereby avoiding infringement.</t>
         </is>
       </c>
     </row>
@@ -537,28 +525,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>C08G 18/12, C09K 3/10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ошибка анализа</t>
+          <t>Composition of a hydrophilic polyurethane based on a water‑soluble polyol (PEG 4 000–10 000 Da, ethoxylated glycerol 800–1 600 Da) reacted with an aliphatic polyisocyanate (2–6 NCO groups) to give a polymer containing ≥85 wt % polymerized ethylene oxide units.  The polyurethane may be blended with a saccharide (≥5 OH, 300–4 000 Da), a dispersant polymer (700–50 000 Da, 10–55 wt % C3–C6 carboxylic acid residues) and/or a surfactant (HLB &gt; 11, 12–100 EO units).  The polymer Mw is 10 000–2 000 000 Da and the terminal log P is –1.5 to 4.5.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Требуется ручной анализ</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Compositions comprising polyether-urethane-urea additives for block resistance and open time 
-       </t>
+          <t>Use a different amine core for the latent hardener – e.g., a tertiary amine such as N,N‑dimethyl‑p‑toluidine or a sterically hindered diamine (e.g., 1,4‑bis(2‑methyl‑2‑propyl)ethane‑1,2‑diamine) that is not listed in the patent.  Employ a latent hardener‑to‑NCO ratio of 0.8–1.0 equivalents (vs. the 1.0–1.2 equivalents implied in the patent) to reduce cross‑link density.  Synthesize the polyether‑urethane‑urea at 120–140 °C for 2–4 h, then dehydrate fillers at 80–100 °C under vacuum (≤0.1 bar) for 30 min.  Add a stabilizer such as 0.1–0.5 wt % 1,1,3,3‑tetramethyl‑2,4‑bis(4‑tert‑butylphenyl)‑1,3‑butanedione (PTSI) or a comparable phosphonate to prevent premature hardening.  Formulate the sealant with a PEG‑based polyol (MW ≈ 8 000 Da), a low‑molecular‑weight aliphatic diisocyanate (MDI or HDI) and the chosen tertiary amine hardener to achieve Shore A 20–25 and elongation &gt;600 % while staying outside the claimed amine cores and ratios.</t>
         </is>
       </c>
     </row>
